--- a/public/词库导入模板.xlsx
+++ b/public/词库导入模板.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -445,10 +445,11 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -484,20 +485,25 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>冠词</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>单元</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>单元主题</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>课文</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>词汇类别</t>
         </is>
@@ -524,32 +530,33 @@
           <t>三明治</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>I had a sandwich for lunch.</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>我午饭吃了个三明治。</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Unit 1</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>食物</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Lesson 1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
@@ -576,32 +583,33 @@
           <t>汤</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
         <is>
           <t>This soup is too hot.</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>这汤太烫了。</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Unit 1</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>食物</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Lesson 1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
@@ -628,32 +636,33 @@
           <t>沙拉</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
         <is>
           <t>She made a green salad.</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>她做了一份蔬菜沙拉。</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Unit 1</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>食物</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Lesson 1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
@@ -680,32 +689,33 @@
           <t>曲奇饼干</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Would you like a cookie?</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>你想来块曲奇吗？</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Unit 1</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>食物</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Lesson 2</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
@@ -732,32 +742,33 @@
           <t>橙汁</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
         <is>
           <t>I drink orange juice every morning.</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>我每天早上喝橙汁。</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Unit 2</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>饮料</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Lesson 3</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Context</t>
         </is>
@@ -784,32 +795,33 @@
           <t>你想要……吗？</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Would you like some tea?</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>你想喝点茶吗？</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Unit 2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>饮料</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Lesson 3</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Extension</t>
         </is>
@@ -826,7 +838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -902,106 +914,110 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" s="3" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6. 冠词</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>西班牙语等有性的语言填 el / la。学西语时卡片上会显示，英语不用填。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>注意</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
       <c r="B8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>语言</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>导入时还要在页面上选一次「这门语言」（英语 / 西班牙语），</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>它决定发音音色和屏幕键盘有没有 ñ 和重音键。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>注意</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>括号注释</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>单词里别写 maths (=mathematics) 这种，写了也会被自动剥掉，注释单独存起来。</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>二选一</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>turn left/right 这种只取前一半作为拼写答案。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>重复词</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>同一个词出现多次，后面的会被跳过（记忆卡按词归一，重复没意义）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>导入之后</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>发音</t>
+          <t>二选一</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>新词库导入后立刻能学，发音先用设备自带的语音。</t>
+          <t>turn left/right 这种只取前一半作为拼写答案。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>重复词</t>
+        </is>
+      </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>想要和内置词库一样的高品质发音，在家长页点「导出词库文件」，</t>
+          <t>同一个词出现多次，后面的会被跳过（记忆卡按词归一，重复没意义）。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>把下载到的 json 放进 word-app/data/ 目录，再跑：</t>
-        </is>
-      </c>
+      <c r="B16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    npm run import-book data/词库id.json</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>导入之后</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>发音</t>
+        </is>
+      </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    npm run audio</t>
+          <t>新词库导入后立刻能学，发音先用设备自带的语音。</t>
         </is>
       </c>
     </row>
@@ -1009,13 +1025,45 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    npm run deploy</t>
+          <t>想要和内置词库一样的高品质发音，在家长页点「导出词库文件」，</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>把下载到的 json 放进 word-app/data/ 目录，再跑：</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    npm run import-book data/词库id.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    npm run audio</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    npm run deploy</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>之后这个词库就有了微软神经网络发音，并且不会再因为清缓存丢失。</t>
         </is>
